--- a/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_HLA ALICANTE.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_HLA ALICANTE.xlsx
@@ -565,13 +565,13 @@
         <v>32</v>
       </c>
       <c r="D2" t="n">
-        <v>70.4766</v>
+        <v>55.9607</v>
       </c>
       <c r="E2" t="n">
-        <v>76.3857</v>
+        <v>62.0338</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.9091</v>
+        <v>-6.073</v>
       </c>
       <c r="G2" t="n">
         <v>-19.5342</v>
@@ -610,13 +610,13 @@
         <v>54.1592</v>
       </c>
       <c r="S2" t="n">
-        <v>19.9276</v>
+        <v>5.4117</v>
       </c>
       <c r="T2" t="n">
-        <v>13.0701</v>
+        <v>-1.2819</v>
       </c>
       <c r="U2" t="n">
-        <v>6.8571</v>
+        <v>6.6935</v>
       </c>
       <c r="V2" t="n">
         <v>61.165</v>
@@ -643,13 +643,13 @@
         <v>27</v>
       </c>
       <c r="D3" t="n">
-        <v>26.8197</v>
+        <v>26.8556</v>
       </c>
       <c r="E3" t="n">
-        <v>25.3219</v>
+        <v>23.1951</v>
       </c>
       <c r="F3" t="n">
-        <v>1.497599999999999</v>
+        <v>3.661</v>
       </c>
       <c r="G3" t="n">
         <v>-4.890899999999999</v>
@@ -688,13 +688,13 @@
         <v>33.0606</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4666</v>
+        <v>2.5028</v>
       </c>
       <c r="T3" t="n">
-        <v>3.8555</v>
+        <v>1.7284</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.3887</v>
+        <v>0.7746000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>15.1053</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>J. WALKER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>23.8346</v>
+        <v>20.6233</v>
       </c>
       <c r="E4" t="n">
-        <v>20.5319</v>
+        <v>15.0632</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3028</v>
+        <v>5.5598</v>
       </c>
       <c r="G4" t="n">
-        <v>6.3626</v>
+        <v>22.5051</v>
       </c>
       <c r="H4" t="n">
-        <v>3.484700000000001</v>
+        <v>-1.558700000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8779</v>
+        <v>24.0635</v>
       </c>
       <c r="J4" t="n">
-        <v>13.0169</v>
+        <v>35.3848</v>
       </c>
       <c r="K4" t="n">
-        <v>8.2538</v>
+        <v>7.985900000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>4.7619</v>
+        <v>27.3989</v>
       </c>
       <c r="M4" t="n">
-        <v>-6.6546</v>
+        <v>-12.8799</v>
       </c>
       <c r="N4" t="n">
-        <v>-4.7697</v>
+        <v>-9.544499999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.8848</v>
+        <v>-3.3353</v>
       </c>
       <c r="P4" t="n">
-        <v>-4.3502</v>
+        <v>-12.833</v>
       </c>
       <c r="Q4" t="n">
-        <v>-24.7954</v>
+        <v>-34.8009</v>
       </c>
       <c r="R4" t="n">
-        <v>20.4451</v>
+        <v>21.968</v>
       </c>
       <c r="S4" t="n">
-        <v>33.5885</v>
+        <v>0.7259999999999998</v>
       </c>
       <c r="T4" t="n">
-        <v>24.8618</v>
+        <v>-1.967</v>
       </c>
       <c r="U4" t="n">
-        <v>8.726699999999999</v>
+        <v>2.6929</v>
       </c>
       <c r="V4" t="n">
-        <v>-11.7663</v>
+        <v>10.2253</v>
       </c>
       <c r="W4" t="n">
-        <v>7.4481</v>
+        <v>16.4466</v>
       </c>
       <c r="X4" t="n">
-        <v>-19.2148</v>
+        <v>-6.2214</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. WALKER</t>
+          <t>T. RICHARDSON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>14.7165</v>
+        <v>7.416100000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>11.1805</v>
+        <v>-4.588</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5359</v>
+        <v>12.0042</v>
       </c>
       <c r="G5" t="n">
-        <v>22.5051</v>
+        <v>0.9034000000000004</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.558700000000001</v>
+        <v>4.829700000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>24.0635</v>
+        <v>-3.9262</v>
       </c>
       <c r="J5" t="n">
-        <v>35.3848</v>
+        <v>9.6442</v>
       </c>
       <c r="K5" t="n">
-        <v>7.985900000000001</v>
+        <v>8.242900000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>27.3989</v>
+        <v>1.4012</v>
       </c>
       <c r="M5" t="n">
-        <v>-12.8799</v>
+        <v>-8.7409</v>
       </c>
       <c r="N5" t="n">
-        <v>-9.544499999999999</v>
+        <v>-3.4135</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.3353</v>
+        <v>-5.327599999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>-12.833</v>
+        <v>5.22</v>
       </c>
       <c r="Q5" t="n">
-        <v>-34.8009</v>
+        <v>-19.1404</v>
       </c>
       <c r="R5" t="n">
-        <v>21.968</v>
+        <v>24.3606</v>
       </c>
       <c r="S5" t="n">
-        <v>-5.181</v>
+        <v>4.1749</v>
       </c>
       <c r="T5" t="n">
-        <v>-5.8497</v>
+        <v>-0.4132999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6684999999999999</v>
+        <v>4.5881</v>
       </c>
       <c r="V5" t="n">
-        <v>10.2253</v>
+        <v>-2.8824</v>
       </c>
       <c r="W5" t="n">
-        <v>16.4466</v>
+        <v>5.321499999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>-6.2214</v>
+        <v>-8.203899999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. RICHARDSON</t>
+          <t>S. CECCARDI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7043</v>
+        <v>5.5397</v>
       </c>
       <c r="E6" t="n">
-        <v>-9.916600000000001</v>
+        <v>3.7407</v>
       </c>
       <c r="F6" t="n">
-        <v>12.6205</v>
+        <v>1.7989</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9034000000000004</v>
+        <v>18.7726</v>
       </c>
       <c r="H6" t="n">
-        <v>4.829700000000001</v>
+        <v>5.0545</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.9262</v>
+        <v>13.7181</v>
       </c>
       <c r="J6" t="n">
-        <v>9.6442</v>
+        <v>25.829</v>
       </c>
       <c r="K6" t="n">
-        <v>8.242900000000001</v>
+        <v>10.4503</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4012</v>
+        <v>15.3786</v>
       </c>
       <c r="M6" t="n">
-        <v>-8.7409</v>
+        <v>-7.0568</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.4135</v>
+        <v>-5.3957</v>
       </c>
       <c r="O6" t="n">
-        <v>-5.327599999999999</v>
+        <v>-1.6609</v>
       </c>
       <c r="P6" t="n">
-        <v>5.22</v>
+        <v>-16.748</v>
       </c>
       <c r="Q6" t="n">
-        <v>-19.1404</v>
+        <v>-37.8461</v>
       </c>
       <c r="R6" t="n">
-        <v>24.3606</v>
+        <v>21.0978</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5371999999999997</v>
+        <v>-0.9732999999999998</v>
       </c>
       <c r="T6" t="n">
-        <v>-5.741400000000001</v>
+        <v>-2.1475</v>
       </c>
       <c r="U6" t="n">
-        <v>5.204400000000001</v>
+        <v>1.1738</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.8824</v>
+        <v>4.4886</v>
       </c>
       <c r="W6" t="n">
-        <v>5.321499999999999</v>
+        <v>17.9052</v>
       </c>
       <c r="X6" t="n">
-        <v>-8.203899999999999</v>
+        <v>-13.4164</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. DAVISON</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4011</v>
+        <v>3.396100000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9282</v>
+        <v>4.0132</v>
       </c>
       <c r="F7" t="n">
-        <v>0.527</v>
+        <v>-0.6164000000000003</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4419</v>
+        <v>6.3626</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8547</v>
+        <v>3.484700000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4128</v>
+        <v>2.8779</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7758</v>
+        <v>13.0169</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2587</v>
+        <v>8.2538</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5172</v>
+        <v>4.7619</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2178</v>
+        <v>-6.6546</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1134</v>
+        <v>-4.7697</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1044</v>
+        <v>-1.8848</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2175</v>
+        <v>-4.3502</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>-24.7954</v>
       </c>
       <c r="R7" t="n">
-        <v>1.305</v>
+        <v>20.4451</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.721</v>
+        <v>13.151</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6165</v>
+        <v>8.3436</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1046</v>
+        <v>4.8073</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5443</v>
+        <v>-11.7663</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>7.4481</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5443</v>
+        <v>-19.2148</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. CECCARDI</t>
+          <t>B. DAVISON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6364000000000019</v>
+        <v>0.1991</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.345700000000001</v>
+        <v>-0.6362</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7096999999999999</v>
+        <v>0.8353</v>
       </c>
       <c r="G8" t="n">
-        <v>18.7726</v>
+        <v>-0.4419</v>
       </c>
       <c r="H8" t="n">
-        <v>5.0545</v>
+        <v>-0.8547</v>
       </c>
       <c r="I8" t="n">
-        <v>13.7181</v>
+        <v>0.4128</v>
       </c>
       <c r="J8" t="n">
-        <v>25.829</v>
+        <v>0.7758</v>
       </c>
       <c r="K8" t="n">
-        <v>10.4503</v>
+        <v>0.2587</v>
       </c>
       <c r="L8" t="n">
-        <v>15.3786</v>
+        <v>0.5172</v>
       </c>
       <c r="M8" t="n">
-        <v>-7.0568</v>
+        <v>-1.2178</v>
       </c>
       <c r="N8" t="n">
-        <v>-5.3957</v>
+        <v>-1.1134</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.6609</v>
+        <v>-0.1044</v>
       </c>
       <c r="P8" t="n">
-        <v>-16.748</v>
+        <v>0.2175</v>
       </c>
       <c r="Q8" t="n">
-        <v>-37.8461</v>
+        <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>21.0978</v>
+        <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>-7.1496</v>
+        <v>-0.1208</v>
       </c>
       <c r="T8" t="n">
-        <v>-7.2344</v>
+        <v>-0.3245</v>
       </c>
       <c r="U8" t="n">
-        <v>0.08470000000000016</v>
+        <v>0.2037</v>
       </c>
       <c r="V8" t="n">
-        <v>4.4886</v>
+        <v>0.5443</v>
       </c>
       <c r="W8" t="n">
-        <v>17.9052</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-13.4164</v>
+        <v>0.5443</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. LLORENTE PAZ</t>
+          <t>M. TORRES CUEVAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.509799999999999</v>
+        <v>-0.2796000000000003</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.599100000000001</v>
+        <v>30.5358</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08909999999999973</v>
+        <v>-30.8152</v>
       </c>
       <c r="G9" t="n">
-        <v>3.2048</v>
+        <v>2.558799999999998</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.1088</v>
+        <v>-15.3397</v>
       </c>
       <c r="I9" t="n">
-        <v>5.3133</v>
+        <v>17.8983</v>
       </c>
       <c r="J9" t="n">
-        <v>5.3732</v>
+        <v>48.4651</v>
       </c>
       <c r="K9" t="n">
-        <v>2.4181</v>
+        <v>9.674799999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9545</v>
+        <v>38.7901</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.1685</v>
+        <v>-45.9064</v>
       </c>
       <c r="N9" t="n">
-        <v>-4.5273</v>
+        <v>-25.0142</v>
       </c>
       <c r="O9" t="n">
-        <v>2.3584</v>
+        <v>-20.8918</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6523999999999996</v>
+        <v>-5.8725</v>
       </c>
       <c r="Q9" t="n">
-        <v>-10.0053</v>
+        <v>-44.5889</v>
       </c>
       <c r="R9" t="n">
-        <v>9.3527</v>
+        <v>38.7158</v>
       </c>
       <c r="S9" t="n">
-        <v>-4.9614</v>
+        <v>-7.2526</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.097</v>
+        <v>-6.9729</v>
       </c>
       <c r="U9" t="n">
-        <v>-2.8647</v>
+        <v>-0.2792000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.1006</v>
+        <v>10.2869</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>33.6329</v>
       </c>
       <c r="X9" t="n">
-        <v>-4.2306</v>
+        <v>-23.3461</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Y. JOSEPH</t>
+          <t>S. LLORENTE PAZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.6124</v>
+        <v>-1.6381</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3071000000000002</v>
+        <v>-3.6488</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.3052</v>
+        <v>2.0105</v>
       </c>
       <c r="G10" t="n">
-        <v>7.5581</v>
+        <v>3.2048</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4197000000000002</v>
+        <v>-2.1088</v>
       </c>
       <c r="I10" t="n">
-        <v>7.1384</v>
+        <v>5.3133</v>
       </c>
       <c r="J10" t="n">
-        <v>12.7166</v>
+        <v>5.3732</v>
       </c>
       <c r="K10" t="n">
-        <v>3.098299999999999</v>
+        <v>2.4181</v>
       </c>
       <c r="L10" t="n">
-        <v>9.618300000000001</v>
+        <v>2.9545</v>
       </c>
       <c r="M10" t="n">
-        <v>-5.1586</v>
+        <v>-2.1685</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.6786</v>
+        <v>-4.5273</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.4801</v>
+        <v>2.3584</v>
       </c>
       <c r="P10" t="n">
-        <v>-7.1778</v>
+        <v>-0.6523999999999996</v>
       </c>
       <c r="Q10" t="n">
-        <v>-16.313</v>
+        <v>-10.0053</v>
       </c>
       <c r="R10" t="n">
-        <v>9.1351</v>
+        <v>9.3527</v>
       </c>
       <c r="S10" t="n">
-        <v>-5.8864</v>
+        <v>-1.0895</v>
       </c>
       <c r="T10" t="n">
-        <v>-4.0558</v>
+        <v>-0.1465000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.8307</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.106199999999999</v>
+        <v>-3.1006</v>
       </c>
       <c r="W10" t="n">
-        <v>7.3449</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>-9.4511</v>
+        <v>-4.2306</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. POLANCO TAVAREZ</t>
+          <t>A. JORDA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.973</v>
+        <v>-2.7585</v>
       </c>
       <c r="E11" t="n">
-        <v>7.479400000000002</v>
+        <v>3.0989</v>
       </c>
       <c r="F11" t="n">
-        <v>-18.4524</v>
+        <v>-5.8574</v>
       </c>
       <c r="G11" t="n">
-        <v>-9.115</v>
+        <v>6.4396</v>
       </c>
       <c r="H11" t="n">
-        <v>-15.9409</v>
+        <v>-9.8765</v>
       </c>
       <c r="I11" t="n">
-        <v>6.825699999999999</v>
+        <v>16.3159</v>
       </c>
       <c r="J11" t="n">
-        <v>10.1505</v>
+        <v>26.1031</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.0844</v>
+        <v>2.103499999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>14.2345</v>
+        <v>23.9987</v>
       </c>
       <c r="M11" t="n">
-        <v>-19.2658</v>
+        <v>-19.6635</v>
       </c>
       <c r="N11" t="n">
-        <v>-11.8566</v>
+        <v>-11.9806</v>
       </c>
       <c r="O11" t="n">
-        <v>-7.4089</v>
+        <v>-7.683000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>-21.5332</v>
+        <v>-0.2176999999999998</v>
       </c>
       <c r="Q11" t="n">
-        <v>-38.0636</v>
+        <v>-36.3234</v>
       </c>
       <c r="R11" t="n">
-        <v>16.5302</v>
+        <v>36.1054</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.6373</v>
+        <v>-4.401999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2606</v>
+        <v>-2.6948</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.377</v>
+        <v>-1.7071</v>
       </c>
       <c r="V11" t="n">
-        <v>22.3123</v>
+        <v>-4.5784</v>
       </c>
       <c r="W11" t="n">
-        <v>36.6529</v>
+        <v>16.0149</v>
       </c>
       <c r="X11" t="n">
-        <v>-14.3406</v>
+        <v>-20.5934</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. BONE</t>
+          <t>Y. JOSEPH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.1395</v>
+        <v>-2.964599999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.244</v>
+        <v>2.5373</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.895300000000001</v>
+        <v>-5.501600000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5379</v>
+        <v>7.5581</v>
       </c>
       <c r="H12" t="n">
-        <v>-16.734</v>
+        <v>0.4197000000000002</v>
       </c>
       <c r="I12" t="n">
-        <v>18.2721</v>
+        <v>7.1384</v>
       </c>
       <c r="J12" t="n">
-        <v>9.8352</v>
+        <v>12.7166</v>
       </c>
       <c r="K12" t="n">
-        <v>-7.8171</v>
+        <v>3.098299999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>17.6522</v>
+        <v>9.618300000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-8.2971</v>
+        <v>-5.1586</v>
       </c>
       <c r="N12" t="n">
-        <v>-8.9169</v>
+        <v>-2.6786</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6197</v>
+        <v>-2.4801</v>
       </c>
       <c r="P12" t="n">
-        <v>3.9152</v>
+        <v>-7.1778</v>
       </c>
       <c r="Q12" t="n">
-        <v>-7.8302</v>
+        <v>-16.313</v>
       </c>
       <c r="R12" t="n">
-        <v>11.7453</v>
+        <v>9.1351</v>
       </c>
       <c r="S12" t="n">
-        <v>-9.2088</v>
+        <v>-1.2384</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.5301</v>
+        <v>-1.2111</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.6787</v>
+        <v>-0.02749999999999997</v>
       </c>
       <c r="V12" t="n">
-        <v>-7.3839</v>
+        <v>-2.106199999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.7189000000000001</v>
+        <v>7.3449</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.664899999999999</v>
+        <v>-9.4511</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I. TAMBA VILLEN</t>
+          <t>J. BONE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.0502</v>
+        <v>-4.7891</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.3109</v>
+        <v>0.01000000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.739199999999999</v>
+        <v>-4.7993</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.7004</v>
+        <v>1.5379</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.955</v>
+        <v>-16.734</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.7453</v>
+        <v>18.2721</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.2426</v>
+        <v>9.8352</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.7008</v>
+        <v>-7.8171</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4579</v>
+        <v>17.6522</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.4579</v>
+        <v>-8.2971</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.2541</v>
+        <v>-8.9169</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.2035</v>
+        <v>0.6197</v>
       </c>
       <c r="P13" t="n">
-        <v>-9.999999999976694e-05</v>
+        <v>3.9152</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9.787599999999999</v>
+        <v>-7.8302</v>
       </c>
       <c r="R13" t="n">
-        <v>9.7875</v>
+        <v>11.7453</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7419</v>
+        <v>-2.8586</v>
       </c>
       <c r="T13" t="n">
-        <v>3.069</v>
+        <v>-1.276</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3272</v>
+        <v>-1.5825</v>
       </c>
       <c r="V13" t="n">
-        <v>-6.091799999999999</v>
+        <v>-7.3839</v>
       </c>
       <c r="W13" t="n">
-        <v>2.6504</v>
+        <v>-0.7189000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.742199999999999</v>
+        <v>-6.664899999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. TORRES CUEVAS</t>
+          <t>E. POLANCO TAVAREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D14" t="n">
-        <v>-14.1533</v>
+        <v>-8.2324</v>
       </c>
       <c r="E14" t="n">
-        <v>23.834</v>
+        <v>8.5863</v>
       </c>
       <c r="F14" t="n">
-        <v>-37.9872</v>
+        <v>-16.8186</v>
       </c>
       <c r="G14" t="n">
-        <v>2.558799999999998</v>
+        <v>-9.115</v>
       </c>
       <c r="H14" t="n">
-        <v>-15.3397</v>
+        <v>-15.9409</v>
       </c>
       <c r="I14" t="n">
-        <v>17.8983</v>
+        <v>6.825699999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>48.4651</v>
+        <v>10.1505</v>
       </c>
       <c r="K14" t="n">
-        <v>9.674799999999999</v>
+        <v>-4.0844</v>
       </c>
       <c r="L14" t="n">
-        <v>38.7901</v>
+        <v>14.2345</v>
       </c>
       <c r="M14" t="n">
-        <v>-45.9064</v>
+        <v>-19.2658</v>
       </c>
       <c r="N14" t="n">
-        <v>-25.0142</v>
+        <v>-11.8566</v>
       </c>
       <c r="O14" t="n">
-        <v>-20.8918</v>
+        <v>-7.4089</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.8725</v>
+        <v>-21.5332</v>
       </c>
       <c r="Q14" t="n">
-        <v>-44.5889</v>
+        <v>-38.0636</v>
       </c>
       <c r="R14" t="n">
-        <v>38.7158</v>
+        <v>16.5302</v>
       </c>
       <c r="S14" t="n">
-        <v>-21.1262</v>
+        <v>0.1033000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-13.6749</v>
+        <v>-0.1536000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-7.4515</v>
+        <v>0.2569</v>
       </c>
       <c r="V14" t="n">
-        <v>10.2869</v>
+        <v>22.3123</v>
       </c>
       <c r="W14" t="n">
-        <v>33.6329</v>
+        <v>36.6529</v>
       </c>
       <c r="X14" t="n">
-        <v>-23.3461</v>
+        <v>-14.3406</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. JORDA RODRIGUEZ</t>
+          <t>I. TAMBA VILLEN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>-20.5212</v>
+        <v>-15.8866</v>
       </c>
       <c r="E15" t="n">
-        <v>-6.8184</v>
+        <v>-8.6814</v>
       </c>
       <c r="F15" t="n">
-        <v>-13.7024</v>
+        <v>-7.204800000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>6.4396</v>
+        <v>-9.7004</v>
       </c>
       <c r="H15" t="n">
-        <v>-9.8765</v>
+        <v>-6.955</v>
       </c>
       <c r="I15" t="n">
-        <v>16.3159</v>
+        <v>-2.7453</v>
       </c>
       <c r="J15" t="n">
-        <v>26.1031</v>
+        <v>-1.2426</v>
       </c>
       <c r="K15" t="n">
-        <v>2.103499999999999</v>
+        <v>-2.7008</v>
       </c>
       <c r="L15" t="n">
-        <v>23.9987</v>
+        <v>1.4579</v>
       </c>
       <c r="M15" t="n">
-        <v>-19.6635</v>
+        <v>-8.4579</v>
       </c>
       <c r="N15" t="n">
-        <v>-11.9806</v>
+        <v>-4.2541</v>
       </c>
       <c r="O15" t="n">
-        <v>-7.683000000000001</v>
+        <v>-4.2035</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2176999999999998</v>
+        <v>-9.999999999976694e-05</v>
       </c>
       <c r="Q15" t="n">
-        <v>-36.3234</v>
+        <v>-9.787599999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>36.1054</v>
+        <v>9.7875</v>
       </c>
       <c r="S15" t="n">
-        <v>-22.1651</v>
+        <v>-0.09430000000000006</v>
       </c>
       <c r="T15" t="n">
-        <v>-12.6129</v>
+        <v>-0.3015000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-9.552099999999999</v>
+        <v>0.2071000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>-4.5784</v>
+        <v>-6.091799999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>16.0149</v>
+        <v>2.6504</v>
       </c>
       <c r="X15" t="n">
-        <v>-20.5934</v>
+        <v>-8.742199999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>29</v>
       </c>
       <c r="D16" t="n">
-        <v>-21.0785</v>
+        <v>-16.3153</v>
       </c>
       <c r="E16" t="n">
-        <v>-20.1069</v>
+        <v>-13.7146</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9721000000000002</v>
+        <v>-2.600000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>-19.8128</v>
@@ -1702,13 +1702,13 @@
         <v>33.2781</v>
       </c>
       <c r="S16" t="n">
-        <v>-9.556799999999999</v>
+        <v>-4.7927</v>
       </c>
       <c r="T16" t="n">
-        <v>-13.8251</v>
+        <v>-7.433400000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>4.2689</v>
+        <v>2.6408</v>
       </c>
       <c r="V16" t="n">
         <v>-0.4092999999999999</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. GEU</t>
+          <t>S. HOLLANDERS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>-21.5589</v>
+        <v>-16.3704</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.710500000000001</v>
+        <v>-2.2055</v>
       </c>
       <c r="F17" t="n">
-        <v>-17.8484</v>
+        <v>-14.165</v>
       </c>
       <c r="G17" t="n">
-        <v>-26.6847</v>
+        <v>-8.1584</v>
       </c>
       <c r="H17" t="n">
-        <v>-13.3189</v>
+        <v>-5.089799999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>-13.3655</v>
+        <v>-3.068700000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3482</v>
+        <v>11.6051</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4340999999999992</v>
+        <v>3.5054</v>
       </c>
       <c r="L17" t="n">
-        <v>0.9135000000000014</v>
+        <v>8.0998</v>
       </c>
       <c r="M17" t="n">
-        <v>-28.033</v>
+        <v>-19.7634</v>
       </c>
       <c r="N17" t="n">
-        <v>-13.7534</v>
+        <v>-8.5953</v>
       </c>
       <c r="O17" t="n">
-        <v>-14.2792</v>
+        <v>-11.1682</v>
       </c>
       <c r="P17" t="n">
-        <v>9.135199999999999</v>
+        <v>2.8275</v>
       </c>
       <c r="Q17" t="n">
-        <v>-22.403</v>
+        <v>-12.8329</v>
       </c>
       <c r="R17" t="n">
-        <v>31.538</v>
+        <v>15.6602</v>
       </c>
       <c r="S17" t="n">
-        <v>12.8843</v>
+        <v>-2.1045</v>
       </c>
       <c r="T17" t="n">
-        <v>5.9618</v>
+        <v>-3.0631</v>
       </c>
       <c r="U17" t="n">
-        <v>6.9224</v>
+        <v>0.9586000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>-16.8937</v>
+        <v>-8.9353</v>
       </c>
       <c r="W17" t="n">
-        <v>11.3826</v>
+        <v>2.0854</v>
       </c>
       <c r="X17" t="n">
-        <v>-28.2763</v>
+        <v>-11.0206</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. HOLLANDERS</t>
+          <t>D. GEU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>-22.7244</v>
+        <v>-27.4597</v>
       </c>
       <c r="E18" t="n">
-        <v>-6.571199999999999</v>
+        <v>-9.190300000000002</v>
       </c>
       <c r="F18" t="n">
-        <v>-16.1533</v>
+        <v>-18.2694</v>
       </c>
       <c r="G18" t="n">
-        <v>-8.1584</v>
+        <v>-26.6847</v>
       </c>
       <c r="H18" t="n">
-        <v>-5.089799999999999</v>
+        <v>-13.3189</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.068700000000001</v>
+        <v>-13.3655</v>
       </c>
       <c r="J18" t="n">
-        <v>11.6051</v>
+        <v>1.3482</v>
       </c>
       <c r="K18" t="n">
-        <v>3.5054</v>
+        <v>0.4340999999999992</v>
       </c>
       <c r="L18" t="n">
-        <v>8.0998</v>
+        <v>0.9135000000000014</v>
       </c>
       <c r="M18" t="n">
-        <v>-19.7634</v>
+        <v>-28.033</v>
       </c>
       <c r="N18" t="n">
-        <v>-8.5953</v>
+        <v>-13.7534</v>
       </c>
       <c r="O18" t="n">
-        <v>-11.1682</v>
+        <v>-14.2792</v>
       </c>
       <c r="P18" t="n">
-        <v>2.8275</v>
+        <v>9.135199999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>-12.8329</v>
+        <v>-22.403</v>
       </c>
       <c r="R18" t="n">
-        <v>15.6602</v>
+        <v>31.538</v>
       </c>
       <c r="S18" t="n">
-        <v>-8.4588</v>
+        <v>6.9836</v>
       </c>
       <c r="T18" t="n">
-        <v>-7.428500000000001</v>
+        <v>0.4819999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0297</v>
+        <v>6.5014</v>
       </c>
       <c r="V18" t="n">
-        <v>-8.9353</v>
+        <v>-16.8937</v>
       </c>
       <c r="W18" t="n">
-        <v>2.0854</v>
+        <v>11.3826</v>
       </c>
       <c r="X18" t="n">
-        <v>-11.0206</v>
+        <v>-28.2763</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>-10.80699999999998</v>
+        <v>23.29630000000002</v>
       </c>
       <c r="E19" t="n">
-        <v>99.87479999999999</v>
+        <v>110.1495</v>
       </c>
       <c r="F19" t="n">
-        <v>-110.682</v>
+        <v>-86.851</v>
       </c>
       <c r="G19" t="n">
         <v>-28.4954</v>
@@ -1933,19 +1933,19 @@
         <v>-404.5604</v>
       </c>
       <c r="R19" t="n">
-        <v>388.2445999999999</v>
+        <v>388.2446</v>
       </c>
       <c r="S19" t="n">
-        <v>-25.9807</v>
+        <v>8.126600000000002</v>
       </c>
       <c r="T19" t="n">
-        <v>-29.1087</v>
+        <v>-18.8331</v>
       </c>
       <c r="U19" t="n">
-        <v>3.127800000000001</v>
+        <v>26.9594</v>
       </c>
       <c r="V19" t="n">
-        <v>59.9798</v>
+        <v>59.97980000000001</v>
       </c>
       <c r="W19" t="n">
         <v>275.7716</v>
